--- a/questionnaire_templates/040_food_preference_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/040_food_preference_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>favorite_cuisine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>main-page</t>
+          <t>What is your favorite type of cuisine?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dietary_preference_1</t>
+          <t>dietary_restrictions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dietary-preference-1</t>
+          <t>Do you have any dietary restrictions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dietary_preference_2</t>
+          <t>eating_schedule</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dietary-preference-2</t>
+          <t>What is your preferred eating schedule?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>breakfast_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>main-page</t>
+          <t>How often do you eat breakfast?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>favorite_meat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>main-page</t>
+          <t>What is your favorite type of meat?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dietary_preference_3</t>
+          <t>flavor_preference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>main-page-2</t>
+          <t>Do you prefer sweet or savory flavors?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>main-page-2</t>
+          <t>Do you have any allergies?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>meals_per_day</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>main-page</t>
+          <t>How many meals do you eat per day?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dietary_preference_4</t>
+          <t>time_of_day</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>main-page-3</t>
+          <t>What is your preferred time of day to eat?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dietary_preference_5</t>
+          <t>special_diets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>main-page-4</t>
+          <t>Do you eat any special diets such as vegan, gluten-free, etc.?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>hunger_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>main-page</t>
+          <t>How do you rate your hunger level after meals?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>eat_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>main-page-5</t>
+          <t>Do you prefer to eat at home or out?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>favorite_food</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>main-page-6</t>
+          <t>What is your favorite type of food?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dietary_preference_6</t>
+          <t>dislikes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>main-page-7</t>
+          <t>Do you have any specific food dislikes?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>food_budget</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>main-page-8</t>
+          <t>How much money do you spend on food per week?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>supplements</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>main-page-9</t>
+          <t>Do you drink any supplements or vitamins?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>meal_beverages</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>main-page-10</t>
+          <t>Do you drink any beverages with meals?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mainpage</t>
+          <t>meals_per_day_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>main-page-11</t>
+          <t>Meals Per Day 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>main-page-12</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>main-page-13</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>main-page-14</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>main-page-15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>main-page-16</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>main-page-17</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mainpage</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>main-page-18</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,170 +965,969 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dietary_preference_1_choices</t>
+          <t>favorite_cuisine_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dietary_preference_1_choices</t>
+          <t>favorite_cuisine_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>european</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>European</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dietary_preference_2_choices</t>
+          <t>favorite_cuisine_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>latin_american</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Latin American</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dietary_preference_2_choices</t>
+          <t>favorite_cuisine_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Indian</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dietary_preference_3_choices</t>
+          <t>favorite_cuisine_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dietary_preference_3_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dietary_preference_4_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dietary_preference_4_choices</t>
+          <t>eating_schedule_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>every_2-3_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Every 2-3 hours</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dietary_preference_6_choices</t>
+          <t>eating_schedule_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>every_3-4_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Every 3-4 hours</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dietary_preference_6_choices</t>
+          <t>eating_schedule_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>every_4-6_hours</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Every 4-6 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>eating_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>every_6-8_hours</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Every 6-8 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eating_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>breakfast_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>breakfast_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3-4_times_a_week</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3-4 times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>breakfast_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>breakfast_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>beef</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lamb</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lamb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>favorite_meat_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>flavor_preference_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sweet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sweet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>flavor_preference_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>savory</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Savory</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>allergies_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>allergies_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>meals_per_day_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>meals_per_day_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>meals_per_day_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>meals_per_day_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>more_than_6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>More than 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>time_of_day_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>time_of_day_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>afternoon</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Afternoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>time_of_day_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>time_of_day_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>late_evening</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Late Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>special_diets_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>special_diets_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hunger_level_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>very_hungry</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Very Hungry</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hunger_level_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>somewhat_hungry</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Somewhat Hungry</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>hunger_level_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>not_hungry</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Not Hungry</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>hunger_level_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>very_not_hungry</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Very Not Hungry</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>eat_location_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>eat_location_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>favorite_food_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>favorite_food_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>salad</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>favorite_food_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>favorite_food_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Burger</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>favorite_food_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dislikes_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dislikes_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>supplements_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>supplements_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>meal_beverages_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>meal_beverages_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>meals_per_day_2_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>meals_per_day_2_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>meals_per_day_2_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>meals_per_day_2_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>more_than_6</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>More than 6</t>
         </is>
       </c>
     </row>
